--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -40323,6 +40323,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1738">
+      <c r="A1738" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1738" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1738" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D1738" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="E1738" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F1738" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G1738" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -40346,6 +40346,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1739">
+      <c r="A1739" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1739" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1739" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D1739" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E1739" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="F1739" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G1739" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1740" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C1740" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D1740" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E1740" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F1740" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="G1740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -40392,6 +40392,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1741">
+      <c r="A1741" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1741" t="n">
+        <v>12600</v>
+      </c>
+      <c r="C1741" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="D1741" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E1741" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="F1741" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="G1741" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -40233,10 +40233,10 @@
     </row>
     <row r="1734">
       <c r="A1734" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1734" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="C1734" t="n">
         <v>2.11999988555908</v>
@@ -40256,13 +40256,13 @@
     </row>
     <row r="1735">
       <c r="A1735" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1735" t="n">
-        <v>4500</v>
+        <v>900</v>
       </c>
       <c r="C1735" t="n">
-        <v>2.14000010490417</v>
+        <v>2.11999988555908</v>
       </c>
       <c r="D1735" t="n">
         <v>2.11999988555908</v>
@@ -40271,7 +40271,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="F1735" t="n">
-        <v>2.14000010490417</v>
+        <v>2.11999988555908</v>
       </c>
       <c r="G1735" t="s">
         <v>7</v>
@@ -40279,22 +40279,22 @@
     </row>
     <row r="1736">
       <c r="A1736" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1736" t="n">
-        <v>1800</v>
+        <v>4500</v>
       </c>
       <c r="C1736" t="n">
-        <v>2.09999990463257</v>
+        <v>2.14000010490417</v>
       </c>
       <c r="D1736" t="n">
-        <v>2.09999990463257</v>
+        <v>2.11999988555908</v>
       </c>
       <c r="E1736" t="n">
-        <v>2.09999990463257</v>
+        <v>2.11999988555908</v>
       </c>
       <c r="F1736" t="n">
-        <v>2.09999990463257</v>
+        <v>2.14000010490417</v>
       </c>
       <c r="G1736" t="s">
         <v>7</v>
@@ -40302,22 +40302,22 @@
     </row>
     <row r="1737">
       <c r="A1737" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1737" t="n">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="C1737" t="n">
-        <v>2.14000010490417</v>
+        <v>2.09999990463257</v>
       </c>
       <c r="D1737" t="n">
-        <v>2.14000010490417</v>
+        <v>2.09999990463257</v>
       </c>
       <c r="E1737" t="n">
-        <v>2.14000010490417</v>
+        <v>2.09999990463257</v>
       </c>
       <c r="F1737" t="n">
-        <v>2.14000010490417</v>
+        <v>2.09999990463257</v>
       </c>
       <c r="G1737" t="s">
         <v>7</v>
@@ -40325,22 +40325,22 @@
     </row>
     <row r="1738">
       <c r="A1738" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1738" t="n">
-        <v>9000</v>
+        <v>900</v>
       </c>
       <c r="C1738" t="n">
-        <v>2.11999988555908</v>
+        <v>2.14000010490417</v>
       </c>
       <c r="D1738" t="n">
-        <v>2.07999992370605</v>
+        <v>2.14000010490417</v>
       </c>
       <c r="E1738" t="n">
-        <v>2.09999990463257</v>
+        <v>2.14000010490417</v>
       </c>
       <c r="F1738" t="n">
-        <v>2.11999988555908</v>
+        <v>2.14000010490417</v>
       </c>
       <c r="G1738" t="s">
         <v>7</v>
@@ -40348,19 +40348,19 @@
     </row>
     <row r="1739">
       <c r="A1739" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1739" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="C1739" t="n">
         <v>2.11999988555908</v>
       </c>
       <c r="D1739" t="n">
-        <v>2.11999988555908</v>
+        <v>2.07999992370605</v>
       </c>
       <c r="E1739" t="n">
-        <v>2.11999988555908</v>
+        <v>2.09999990463257</v>
       </c>
       <c r="F1739" t="n">
         <v>2.11999988555908</v>
@@ -40371,22 +40371,22 @@
     </row>
     <row r="1740">
       <c r="A1740" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1740" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="C1740" t="n">
-        <v>2.14000010490417</v>
+        <v>2.11999988555908</v>
       </c>
       <c r="D1740" t="n">
-        <v>2.14000010490417</v>
+        <v>2.11999988555908</v>
       </c>
       <c r="E1740" t="n">
-        <v>2.14000010490417</v>
+        <v>2.11999988555908</v>
       </c>
       <c r="F1740" t="n">
-        <v>2.14000010490417</v>
+        <v>2.11999988555908</v>
       </c>
       <c r="G1740" t="s">
         <v>7</v>
@@ -40394,24 +40394,47 @@
     </row>
     <row r="1741">
       <c r="A1741" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1741" t="n">
-        <v>12600</v>
+        <v>4500</v>
       </c>
       <c r="C1741" t="n">
-        <v>2.16000008583069</v>
+        <v>2.14000010490417</v>
       </c>
       <c r="D1741" t="n">
-        <v>2.11999988555908</v>
+        <v>2.14000010490417</v>
       </c>
       <c r="E1741" t="n">
-        <v>2.11999988555908</v>
+        <v>2.14000010490417</v>
       </c>
       <c r="F1741" t="n">
-        <v>2.16000008583069</v>
+        <v>2.14000010490417</v>
       </c>
       <c r="G1741" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1742" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C1742" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D1742" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E1742" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F1742" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="G1742" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -40417,24 +40417,47 @@
     </row>
     <row r="1742">
       <c r="A1742" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1742" t="n">
+        <v>12600</v>
+      </c>
+      <c r="C1742" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="D1742" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E1742" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="F1742" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="G1742" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="1" t="n">
         <v>46283.2916666667</v>
       </c>
-      <c r="B1742" t="n">
+      <c r="B1743" t="n">
         <v>1800</v>
       </c>
-      <c r="C1742" t="n">
+      <c r="C1743" t="n">
         <v>2.14000010490417</v>
       </c>
-      <c r="D1742" t="n">
+      <c r="D1743" t="n">
         <v>2.14000010490417</v>
       </c>
-      <c r="E1742" t="n">
+      <c r="E1743" t="n">
         <v>2.14000010490417</v>
       </c>
-      <c r="F1742" t="n">
+      <c r="F1743" t="n">
         <v>2.14000010490417</v>
       </c>
-      <c r="G1742" t="s">
+      <c r="G1743" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -45745,6 +45745,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1746">
+      <c r="A1746" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1746" t="n">
+        <v>12600</v>
+      </c>
+      <c r="C1746" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="D1746" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="E1746" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="F1746" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="G1746" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="H1746" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -45771,6 +45771,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1747">
+      <c r="A1747" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1747" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C1747" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="D1747" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="E1747" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F1747" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="G1747" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="H1747" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -40553,6 +40553,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1748">
+      <c r="A1748" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1748" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1748" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="D1748" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="E1748" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F1748" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="G1748" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -40622,6 +40622,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1751">
+      <c r="A1751" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1751" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1751" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D1751" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E1751" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F1751" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="G1751" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B1752" t="n">
+        <v>9900</v>
+      </c>
+      <c r="C1752" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D1752" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="E1752" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F1752"/>
+      <c r="G1752" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -40661,7 +40661,9 @@
       <c r="E1752" t="n">
         <v>2.09999990463257</v>
       </c>
-      <c r="F1752"/>
+      <c r="F1752" t="n">
+        <v>2.09999990463257</v>
+      </c>
       <c r="G1752" t="s">
         <v>7</v>
       </c>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -40668,6 +40668,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1753">
+      <c r="A1753" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1753" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1753" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D1753" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E1753" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F1753" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="G1753" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1754" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C1754" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D1754" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E1754" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="F1754"/>
+      <c r="G1754" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -40707,7 +40707,9 @@
       <c r="E1754" t="n">
         <v>2.11999988555908</v>
       </c>
-      <c r="F1754"/>
+      <c r="F1754" t="n">
+        <v>2.11999988555908</v>
+      </c>
       <c r="G1754" t="s">
         <v>7</v>
       </c>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -40714,6 +40714,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1755">
+      <c r="A1755" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1755" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1755" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D1755" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E1755" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="F1755" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G1755" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1756" t="n">
+        <v>8100</v>
+      </c>
+      <c r="C1756" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="D1756" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="E1756" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="F1756"/>
+      <c r="G1756" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -40753,8 +40753,31 @@
       <c r="E1756" t="n">
         <v>2.03999996185303</v>
       </c>
-      <c r="F1756"/>
+      <c r="F1756" t="n">
+        <v>2.1800000667572</v>
+      </c>
       <c r="G1756" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1757" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C1757" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="D1757" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E1757" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="F1757"/>
+      <c r="G1757" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -40776,7 +40776,9 @@
       <c r="E1757" t="n">
         <v>2.16000008583069</v>
       </c>
-      <c r="F1757"/>
+      <c r="F1757" t="n">
+        <v>2.14000010490417</v>
+      </c>
       <c r="G1757" t="s">
         <v>7</v>
       </c>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -40806,6 +40806,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1759">
+      <c r="A1759" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1759" t="n">
+        <v>6300</v>
+      </c>
+      <c r="C1759" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="D1759" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E1759" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F1759" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="G1759" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -40829,6 +40829,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1760">
+      <c r="A1760" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B1760" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C1760" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="D1760" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E1760" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="F1760" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="G1760" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -46187,6 +46187,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1763">
+      <c r="A1763" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1763" t="n">
+        <v>900</v>
+      </c>
+      <c r="C1763" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="D1763" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="E1763" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="F1763" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="G1763" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="H1763" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -51505,6 +51505,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1764">
+      <c r="A1764" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1764" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1764" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D1764" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E1764" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1764" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="G1764" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="H1764" t="n">
+        <v>16200</v>
+      </c>
+      <c r="I1764" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1765" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1765" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="D1765" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E1765" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F1765" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="G1765" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="H1765" t="n">
+        <v>24300</v>
+      </c>
+      <c r="I1765" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -51563,6 +51563,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1766">
+      <c r="A1766" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1766" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1766" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="D1766" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="E1766" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="F1766" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="G1766" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="H1766" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1766" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1767" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1767" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D1767" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E1767" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F1767" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="G1767" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="H1767" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I1767" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -51621,6 +51621,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1768">
+      <c r="A1768" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1768" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1768" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="D1768" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E1768" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F1768" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="G1768" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="H1768" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I1768" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -51650,6 +51650,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1769">
+      <c r="A1769" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1769" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1769" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="D1769" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E1769" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="F1769" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="G1769" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="H1769" t="n">
+        <v>5400</v>
+      </c>
+      <c r="I1769" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -51679,6 +51679,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1770">
+      <c r="A1770" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1770" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1770" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D1770" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E1770" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F1770" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="G1770" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="H1770" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1770" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1771" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1771" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D1771" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E1771" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="F1771" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="G1771" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="H1771" t="n">
+        <v>13500</v>
+      </c>
+      <c r="I1771" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -51737,6 +51737,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1772">
+      <c r="A1772" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1772" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1772" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="D1772" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E1772" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F1772" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="G1772" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="H1772" t="n">
+        <v>13500</v>
+      </c>
+      <c r="I1772" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFT.MI.xlsx
+++ b/data/MFT.MI.xlsx
@@ -51766,6 +51766,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1773">
+      <c r="A1773" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1773" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1773" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="D1773" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E1773" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="F1773" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="G1773" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="H1773" t="n">
+        <v>10800</v>
+      </c>
+      <c r="I1773" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
